--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/ba-integration-hard.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/ba-integration-hard.xlsx
@@ -524,19 +524,19 @@
         <v>Đây là bài toán kinh điển trong tích hợp dữ liệu. BA phải cung cấp quy tắc logic xử lý chuỗi rõ ràng (Transformation Rule), bao gồm cả cách xử lý các trường hợp đặc biệt (như tên nước ngoài, tên chỉ có 2 từ, hoặc tên có nhiều hơn 4 từ) để dev triển khai chính xác.</v>
       </c>
       <c r="F4" t="str">
-        <v>Đặc tả quy tắc xử lý chuỗi (String Manipulation): Khi truyền từ A sang B, viết thuật toán tách chuỗi `fullName` dựa trên khoảng trắng để phân bổ vào `firstName`, `lastName`, `middleName` và ngược lại khi truyền từ B sang A thì thực hiện ghép chuỗi kèm khoảng trắng — quy tắc tách ghép chuỗi nghiệp vụ</v>
+        <v>Chỉ ánh xạ trường `fullName` sang trường `firstName` của hệ thống B, bỏ trống hoàn toàn các trường `lastName` và `middleName` — chấp nhận mất mát dữ liệu</v>
       </c>
       <c r="G4" t="str">
         <v>Yêu cầu hệ thống B đập đi xây lại cấu trúc database để gộp 3 trường thành 1 trường `fullName` duy nhất cho giống hệ thống A — đập đi xây lại hệ thống</v>
       </c>
       <c r="H4" t="str">
-        <v>Chỉ ánh xạ trường `fullName` sang trường `firstName` của hệ thống B, bỏ trống hoàn toàn các trường `lastName` và `middleName` — chấp nhận mất mát dữ liệu</v>
+        <v>Đặc tả quy tắc xử lý chuỗi (String Manipulation): Khi truyền từ A sang B, viết thuật toán tách chuỗi `fullName` dựa trên khoảng trắng để phân bổ vào `firstName`, `lastName`, `middleName` và ngược lại khi truyền từ B sang A thì thực hiện ghép chuỗi kèm khoảng trắng — quy tắc tách ghép chuỗi nghiệp vụ</v>
       </c>
       <c r="I4" t="str">
         <v>Yêu cầu khách hàng tự thực hiện chuẩn hóa dữ liệu bằng tay trước khi hệ thống thực hiện truyền tải API — chuyển giao công việc</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -559,13 +559,13 @@
         <v>Thiết kế đối soát 3 bước: Đối soát số lượng bản ghi (Record count), Đối soát tổng số tiền lũy kế (Hash totals/Financial totals) ở cả nguồn và đích, và Đối soát ngẫu nhiên chi tiết từng giao dịch của các tài khoản VIP — đối soát toàn vẹn đa tầng</v>
       </c>
       <c r="G5" t="str">
+        <v>Yêu cầu lập trình viên tự viết một đoạn mã tự động sửa số dư tài khoản của hệ thống mới cho khớp với số dư hệ thống cũ — sửa dữ liệu cưỡng bức</v>
+      </c>
+      <c r="H5" t="str">
         <v>Chỉ cần đếm xem tổng số dòng ở bảng nguồn có bằng tổng số dòng ở bảng đích sau khi chuyển đổi xong hay không — đối soát số lượng đơn giản</v>
       </c>
-      <c r="H5" t="str">
+      <c r="I5" t="str">
         <v>Châm ngòi chạy thử hệ thống mới, nếu khách hàng nào gọi điện lên tổng đài báo mất tiền thì mới kiểm tra lại tài khoản đó — đối soát thụ động</v>
-      </c>
-      <c r="I5" t="str">
-        <v>Yêu cầu lập trình viên tự viết một đoạn mã tự động sửa số dư tài khoản của hệ thống mới cho khớp với số dư hệ thống cũ — sửa dữ liệu cưỡng bức</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -588,19 +588,19 @@
         <v>Trong tích hợp thanh toán, do lỗi mạng, hệ thống gửi request có thể gửi lại (retry). Nếu API không có tính Idempotency (bằng cách kiểm tra Idempotency Key duy nhất của giao dịch), hệ thống đích có thể xử lý trùng lặp, dẫn đến việc trừ tiền khách hàng 2 lần.</v>
       </c>
       <c r="F6" t="str">
+        <v>Để đảm bảo mật khẩu của khách hàng được thay đổi liên tục sau mỗi lần gọi API thanh toán thành công — bảo mật mật khẩu</v>
+      </c>
+      <c r="G6" t="str">
         <v>Để đảm bảo rằng nếu một API gọi thanh toán bị gửi trùng lặp nhiều lần (do mạng chập chờn, người dùng bấm nút nhiều lần), hệ thống chỉ thực hiện trừ tiền duy nhất một lần — ngăn chặn trừ tiền trùng lặp</v>
-      </c>
-      <c r="G6" t="str">
-        <v>Để tự động tăng gấp đôi số tiền thanh toán nếu khách hàng thực hiện giao dịch vào giờ cao điểm của hệ thống — tăng doanh thu</v>
       </c>
       <c r="H6" t="str">
         <v>Để nén kích thước dữ liệu gửi đi qua mạng giúp API phản hồi nhanh hơn gấp 10 lần — tối ưu hóa tốc độ</v>
       </c>
       <c r="I6" t="str">
-        <v>Để đảm bảo mật khẩu của khách hàng được thay đổi liên tục sau mỗi lần gọi API thanh toán thành công — bảo mật mật khẩu</v>
+        <v>Để tự động tăng gấp đôi số tiền thanh toán nếu khách hàng thực hiện giao dịch vào giờ cao điểm của hệ thống — tăng doanh thu</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -620,19 +620,19 @@
         <v>SOAP là giao thức chuẩn hóa cao, bảo mật mạnh mẽ (WS-Security) và có file định nghĩa cấu trúc WSDL (Web Services Description Language) giúp validate dữ liệu chặt chẽ ở tầng XML. REST là phong cách kiến trúc nhẹ nhàng hơn, dùng JSON giúp giảm dung lượng mạng truyền tải, phù hợp cho Web/Mobile.</v>
       </c>
       <c r="F7" t="str">
+        <v>SOAP chỉ dành cho lập trình viên Java dùng; còn REST dành riêng cho lập trình viên Javascript — giới hạn công nghệ</v>
+      </c>
+      <c r="G7" t="str">
+        <v>SOAP không hỗ trợ bất kỳ phương thức bảo mật nào; còn REST bắt buộc sử dụng mã hóa HTTPS — so sánh bảo mật</v>
+      </c>
+      <c r="H7" t="str">
         <v>SOAP bắt buộc sử dụng định dạng XML và có tài liệu định nghĩa WSDL chặt chẽ; REST linh hoạt hỗ trợ nhiều định dạng (thường dùng JSON) và nhẹ hơn — SOAP XML WSDL vs REST JSON</v>
       </c>
-      <c r="G7" t="str">
+      <c r="I7" t="str">
         <v>SOAP chỉ chạy qua giao thức truyền file FTP; còn REST chạy qua giao thức HTTP thường — phương thức truyền tải</v>
       </c>
-      <c r="H7" t="str">
-        <v>SOAP không hỗ trợ bất kỳ phương thức bảo mật nào; còn REST bắt buộc sử dụng mã hóa HTTPS — so sánh bảo mật</v>
-      </c>
-      <c r="I7" t="str">
-        <v>SOAP chỉ dành cho lập trình viên Java dùng; còn REST dành riêng cho lập trình viên Javascript — giới hạn công nghệ</v>
-      </c>
       <c r="J7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -652,19 +652,19 @@
         <v>Khi tích hợp với bên thứ ba có Rate Limiting, hệ thống của bạn phải kiểm soát tần suất gửi (Throttling). Sử dụng Message Queue (như RabbitMQ/ActiveMQ) giúp lưu trữ tạm thời yêu cầu và xử lý tuần tự (Rate-limiting consumer), đảm bảo không mất mát dữ liệu đơn hàng và không vi phạm chính sách của đối tác.</v>
       </c>
       <c r="F8" t="str">
+        <v>Yêu cầu lập trình viên viết code bỏ qua giới hạn Rate Limit của đối tác bằng cách sử dụng các tài khoản IP giả mạo — gian lận IP</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Gửi liên tục các request cho đến khi API của đối tác bị sập hoàn toàn và họ buộc phải mở khóa giới hạn — tấn công từ chối dịch vụ</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Khi hệ thống báo lỗi Rate Limit, tự động hiển thị thông báo lỗi lên màn hình và yêu cầu khách hàng tự quay lại mua hàng sau 1 tiếng — đẩy lỗi cho khách hàng</v>
+      </c>
+      <c r="I8" t="str">
         <v>Thiết kế hàng đợi tin nhắn (Message Queue) để lưu trữ các yêu cầu đẩy đơn sang đối tác, kết hợp cơ chế Worker chạy ngầm để lấy dần yêu cầu và gọi API đối tác với tần suất nằm trong giới hạn cho phép — hàng đợi kiểm soát Rate Limit</v>
       </c>
-      <c r="G8" t="str">
-        <v>Khi hệ thống báo lỗi Rate Limit, tự động hiển thị thông báo lỗi lên màn hình và yêu cầu khách hàng tự quay lại mua hàng sau 1 tiếng — đẩy lỗi cho khách hàng</v>
-      </c>
-      <c r="H8" t="str">
-        <v>Gửi liên tục các request cho đến khi API của đối tác bị sập hoàn toàn và họ buộc phải mở khóa giới hạn — tấn công từ chối dịch vụ</v>
-      </c>
-      <c r="I8" t="str">
-        <v>Yêu cầu lập trình viên viết code bỏ qua giới hạn Rate Limit của đối tác bằng cách sử dụng các tài khoản IP giả mạo — gian lận IP</v>
-      </c>
       <c r="J8">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -684,19 +684,19 @@
         <v>SSO qua SAML 2.0 hoạt động dựa trên cơ chế tin cậy bằng chữ ký số. Người dùng không gửi mật khẩu cho SP. SP tin tưởng vào SAML Assertion (khẳng định xác thực) do IdP ký và gửi về qua trình duyệt. BA phải mô tả luồng đi của Assertion này để các bên cấu hình đúng hệ thống.</v>
       </c>
       <c r="F9" t="str">
+        <v>Đặc tả cách thức cơ sở dữ liệu của IdP tự động đồng bộ hóa mật khẩu dạng rõ (plaintext) sang cơ sở dữ liệu của SP — đồng bộ mật khẩu thô</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Đặc tả cách cài đặt phần mềm quản lý cookie của bên thứ ba lên trình duyệt của tất cả nhân viên — cài đặt phần mềm</v>
+      </c>
+      <c r="H9" t="str">
         <v>Đặc tả luồng điều hướng (Redirect) của trình duyệt người dùng, cách SP gửi AuthnRequest tới IdP, cách IdP xác thực người dùng và trả lại SAML Assertion chứa thông tin người dùng được ký số về cho SP — đặc tả luồng xác thực liên kết SAML</v>
-      </c>
-      <c r="G9" t="str">
-        <v>Đặc tả cách thức cơ sở dữ liệu của IdP tự động đồng bộ hóa mật khẩu dạng rõ (plaintext) sang cơ sở dữ liệu của SP — đồng bộ mật khẩu thô</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Đặc tả cách cài đặt phần mềm quản lý cookie của bên thứ ba lên trình duyệt của tất cả nhân viên — cài đặt phần mềm</v>
       </c>
       <c r="I9" t="str">
         <v>Đặc tả luồng mã hóa ổ cứng của máy chủ lưu trữ dữ liệu người dùng ở cả hai công ty — mã hóa ổ cứng</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -716,7 +716,7 @@
         <v>ETL biến đổi dữ liệu bên ngoài rồi mới nạp vào. Khi dữ liệu cực lớn, máy chủ ETL dễ bị nghẽn cổ chai. ELT (như Snowflake, BigQuery) nạp dữ liệu thô vào trước (Extract &amp; Load), sau đó dùng SQL chạy trực tiếp trên kho dữ liệu phân tán (Transform) giúp xử lý nhanh và linh hoạt hơn nhiều.</v>
       </c>
       <c r="F10" t="str">
-        <v>ETL biến đổi dữ liệu trên máy chủ trung gian trước khi nạp vào kho; ELT nạp dữ liệu thô thẳng vào kho rồi tận dụng sức mạnh tính toán phân tán của Data Warehouse để biến đổi dữ liệu — biến đổi trước vs biến đổi sau</v>
+        <v>ETL bắt buộc phải chạy trên máy chủ vật lý đặt tại văn phòng; còn ELT chỉ chạy được trên điện thoại di động — hạ tầng chạy</v>
       </c>
       <c r="G10" t="str">
         <v>ETL chỉ hỗ trợ dữ liệu từ file Excel; còn ELT chỉ hỗ trợ dữ liệu từ các thiết bị cảm biến IoT — phân loại nguồn dữ liệu</v>
@@ -725,10 +725,10 @@
         <v>ETL yêu cầu lập trình viên phải viết code tay bằng ngôn ngữ C++; còn ELT tự động sinh code bằng trí tuệ nhân tạo — ngôn ngữ lập trình</v>
       </c>
       <c r="I10" t="str">
-        <v>ETL bắt buộc phải chạy trên máy chủ vật lý đặt tại văn phòng; còn ELT chỉ chạy được trên điện thoại di động — hạ tầng chạy</v>
+        <v>ETL biến đổi dữ liệu trên máy chủ trung gian trước khi nạp vào kho; ELT nạp dữ liệu thô thẳng vào kho rồi tận dụng sức mạnh tính toán phân tán của Data Warehouse để biến đổi dữ liệu — biến đổi trước vs biến đổi sau</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -748,19 +748,19 @@
         <v>Tích hợp hệ thống yêu cầu xử lý lỗi mượt mà (Graceful Degradation). Nếu API chỉ trả về mã lỗi HTTP chung chung (như 400 hoặc 500) mà không có Error Code và Message chi tiết trong Response Body, hệ thống gọi API sẽ không thể biết nguyên nhân cụ thể để có kịch bản xử lý tự động phù hợp.</v>
       </c>
       <c r="F11" t="str">
+        <v>Để chứng minh cho khách hàng thấy rằng hệ thống của đối tác luôn luôn gặp nhiều lỗi hơn hệ thống của mình — quy trách nhiệm lỗi</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Để tự động khóa tài khoản của người dùng nếu họ gọi API gặp bất kỳ lỗi nào từ phía máy chủ — khóa tài khoản người dùng</v>
+      </c>
+      <c r="H11" t="str">
         <v>Để hệ thống gọi API có thể tự động phân tích mã lỗi (Error Code) cụ thể và đưa ra hành vi xử lý phù hợp (ví dụ: hiển thị thông báo thân thiện cho người dùng hoặc tự động thử lại khi gặp lỗi mạng) — xử lý lỗi tự động thông minh</v>
-      </c>
-      <c r="G11" t="str">
-        <v>Để chứng minh cho khách hàng thấy rằng hệ thống của đối tác luôn luôn gặp nhiều lỗi hơn hệ thống của mình — quy trách nhiệm lỗi</v>
-      </c>
-      <c r="H11" t="str">
-        <v>Để tự động khóa tài khoản của người dùng nếu họ gọi API gặp bất kỳ lỗi nào từ phía máy chủ — khóa tài khoản người dùng</v>
       </c>
       <c r="I11" t="str">
         <v>Để đảm bảo mã nguồn của API tự động sửa lỗi và chạy lại thành công mà không cần lập trình viên can thiệp — tự sửa lỗi</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
